--- a/docs/design/03系统需求分析/VerdantOS系统需求分析表.xlsx
+++ b/docs/design/03系统需求分析/VerdantOS系统需求分析表.xlsx
@@ -1,31 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\VerdantOS\docs\design\03系统需求分析\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08BB113-6CBB-4A1A-9EA1-AC393F720E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="example" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+  <si>
+    <t>用户功能</t>
+  </si>
+  <si>
+    <t>系统需要解决的问题</t>
+  </si>
+  <si>
+    <t>涉及部分</t>
+  </si>
+  <si>
+    <t>查看环境状态</t>
+  </si>
+  <si>
+    <t>如何获取空气温湿度和光照数据？</t>
+  </si>
+  <si>
+    <t>传感器、STM32</t>
+  </si>
+  <si>
+    <t>如何将数据传输到PC？</t>
+  </si>
+  <si>
+    <t>STM32、UART、PC</t>
+  </si>
+  <si>
+    <t>自动补光</t>
+  </si>
+  <si>
+    <t>如何判断是否达到补光条件？</t>
+  </si>
+  <si>
+    <t>配置模块、状态机</t>
+  </si>
+  <si>
+    <t>如何控制补光灯？</t>
+  </si>
+  <si>
+    <t>STM32、GPIO、执行器</t>
+  </si>
+  <si>
+    <t>如何实现“亮20秒后关闭”？</t>
+  </si>
+  <si>
+    <t>RTOS、定时机制</t>
+  </si>
+  <si>
+    <t>修改养护配置</t>
+  </si>
+  <si>
+    <t>配置保存在哪里？</t>
+  </si>
+  <si>
+    <t>Qt、配置模块</t>
+  </si>
+  <si>
+    <t>修改配置后如何让运行中的系统使用新配置？</t>
+  </si>
+  <si>
+    <t>配置热加载</t>
+  </si>
+  <si>
+    <t>查看Log</t>
+  </si>
+  <si>
+    <t>谁产生日志、在哪里保存？</t>
+  </si>
+  <si>
+    <t>PC、日志模块</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,11 +147,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +434,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="69" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>